--- a/jpcore-r4/main/StructureDefinition-jp-patient.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-patient.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -317,16 +317,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -452,7 +452,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -632,19 +632,19 @@
     <t>usual | official | temp | secondary | old (If known) 【詳細参照】</t>
   </si>
   <si>
-    <t>この識別子の目的。 / The purpose of this identifier.</t>
+    <t>このidentifierの目的。 / The purpose of this identifier.</t>
   </si>
   <si>
     <t>IDの種別をValueSet(IdentifierUse)より選択する。  - usual : 一般- official : 公式（マイナンバーなど、最も信頼できると見なされる場合に使用）- temp : 一時的　- secondary : 二次利用　- old : 過去の識別子</t>
   </si>
   <si>
-    <t>特定の使用のコンテキストが一連の識別子の中から選択される適切な識別子を許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>既知の場合、この識別子の目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
+    <t>既知の場合、このidentifierの目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
@@ -666,19 +666,19 @@
     <t>識別子の種別 【詳細参照】</t>
   </si>
   <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
     <t>IDの種別をValueSet(Identifier Type Codes)より選択する。　- DL : 運転免許証番号　- PPN : パスポート番号　- BRN : 血統登録番号　- MR : カルテ番号、など</t>
   </si>
   <si>
-    <t>識別子システムが不明な場合、ユーザーは識別子を使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
@@ -702,7 +702,7 @@
     <t>Patient.identifier.system には、urn:oid:1.2.392.100495.20.3.51.医療機関識別OID番号を使用する。 医療機関識別OID番号は患者IDの発行者である機関の医療機関コード（１０桁）の先頭に１をつけた11桁とする。医療機関コード（１０桁）の詳細はOrganizationプロファイルの医療機関コード１０桁の説明を参照すること。  ```例：医療機関コード「1312345670」の場合「urn:oid:1.2.392.100495.20.3.51.11312345670」```　なお、urn:oid:1.2.392.100495.20.3.51の部分は、「[処方情報 HL7FHIR 記述仕様](https://std.jpfhir.jp/stddoc/ePrescriptionDataFHIR_v1x.pdf)」表19 識別子名前空間一覧において医療機関等の患者IDとして割り当てられたOIDのURL型である。地域医療連携ネットワークの地域患者IDを指定する場合も同様に、地域患者IDを識別する名前空間（IHE ITI PIX等で使用されるOID等）をsystemに使用することができる。</t>
   </si>
   <si>
-    <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -720,7 +720,7 @@
     <t>識別子のvalueは一意である必要がある。 【詳細参照】</t>
   </si>
   <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
     <t>患者を一意的に識別するID(例えば、患者IDやカルテ番号など)を設定。</t>
@@ -745,7 +745,7 @@
     <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
   </si>
   <si>
-    <t>識別子が使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>IDが使われていた/使われている期間。</t>
@@ -770,7 +770,7 @@
     <t>IDを発行した組織（単なるテキストである可能性があります） / Organization that issued id (may be just text)</t>
   </si>
   <si>
-    <t>識別子を発行/管理する組織。 / Organization that issued/manages the identifier.</t>
+    <t>identifierを発行/管理する組織。 / Organization that issued/manages the identifier.</t>
   </si>
   <si>
     <t>IDを発行した組織（テキストのみでも可）</t>
@@ -822,7 +822,7 @@
 </t>
   </si>
   <si>
-    <t>人の名前情報、その一部分と使い方</t>
+    <t>患者に関連付けられた名前 / A name associated with the patient</t>
   </si>
   <si>
     <t>個人に関連付けられた名前。</t>
@@ -840,10 +840,13 @@
     <t>複数の名前で患者を追跡できる必要がある。例としては、正式名とパートナー名がある。</t>
   </si>
   <si>
-    <t>EN (actually, PN)</t>
-  </si>
-  <si>
-    <t>XPN</t>
+    <t>name</t>
+  </si>
+  <si>
+    <t>.patient.name</t>
+  </si>
+  <si>
+    <t>PID-5, PID-9</t>
   </si>
   <si>
     <t>Patient.telecom</t>
@@ -967,7 +970,7 @@
     <t>home | work | temp | old | mobile - 連絡先の用途等 【詳細参照】</t>
   </si>
   <si>
-    <t>「接点の目的を特定する。」</t>
+    <t>接点の目的を特定する。</t>
   </si>
   <si>
     <t>患者の連絡先の種別をValueSet(ContactPointUse)より選択する。   一時的なものまたは古いものであると明示しない限り、連絡先が最新とみなされる。  
@@ -981,7 +984,7 @@
     <t>Need to track the way a person uses this contact, so a user can choose which is appropriate for their purpose.</t>
   </si>
   <si>
-    <t>「接点の使用。」</t>
+    <t>接点の使用。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/contact-point-use|4.0.1</t>
@@ -1535,7 +1538,7 @@
     <t>患者について連絡できる人を確認する必要がある。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 pat-1:少なくとも連絡先の詳細または組織への参照を含めるものとする / SHALL at least contain a contact's details or a reference to an organization {name.exists() or telecom.exists() or address.exists() or organization.exists()}</t>
   </si>
   <si>
@@ -1614,9 +1617,6 @@
   </si>
   <si>
     <t>連絡先は名前で識別する必要があるが、その連絡先に複数の名前が必要になることはまれである。</t>
-  </si>
-  <si>
-    <t>name</t>
   </si>
   <si>
     <t>NK1-2</t>
@@ -2232,7 +2232,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="145.265625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="155.12109375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="51.921875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -4984,7 +4984,7 @@
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
         <v>252</v>
@@ -5057,7 +5057,7 @@
         <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>161</v>
+        <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>102</v>
@@ -5066,13 +5066,13 @@
         <v>257</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>82</v>
+        <v>258</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -5080,10 +5080,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5106,19 +5106,19 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5167,7 +5167,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5182,16 +5182,16 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
@@ -5199,10 +5199,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5228,10 +5228,10 @@
         <v>180</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5314,10 +5314,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5343,13 +5343,13 @@
         <v>135</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5390,7 +5390,7 @@
         <v>138</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>82</v>
@@ -5411,7 +5411,7 @@
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>184</v>
@@ -5431,10 +5431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5460,13 +5460,13 @@
         <v>110</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5495,10 +5495,10 @@
         <v>195</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5516,7 +5516,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5525,13 +5525,13 @@
         <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>82</v>
@@ -5540,7 +5540,7 @@
         <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -5548,10 +5548,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5577,16 +5577,16 @@
         <v>180</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5635,7 +5635,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5647,10 +5647,10 @@
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>82</v>
@@ -5659,7 +5659,7 @@
         <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5667,10 +5667,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5696,16 +5696,16 @@
         <v>110</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5733,10 +5733,10 @@
         <v>195</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
@@ -5754,7 +5754,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5766,10 +5766,10 @@
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>82</v>
@@ -5778,7 +5778,7 @@
         <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -5786,10 +5786,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5812,16 +5812,16 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5871,7 +5871,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5883,7 +5883,7 @@
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>184</v>
@@ -5903,10 +5903,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5932,13 +5932,13 @@
         <v>227</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5988,7 +5988,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6000,10 +6000,10 @@
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>82</v>
@@ -6020,10 +6020,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6049,16 +6049,16 @@
         <v>110</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6086,10 +6086,10 @@
         <v>195</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -6107,7 +6107,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6122,16 +6122,16 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6139,10 +6139,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6165,19 +6165,19 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6226,7 +6226,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6241,27 +6241,27 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6284,19 +6284,19 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6345,7 +6345,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6360,7 +6360,7 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>184</v>
@@ -6369,7 +6369,7 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6377,10 +6377,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6403,19 +6403,19 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6464,7 +6464,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6479,16 +6479,16 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6496,10 +6496,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6611,10 +6611,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6728,10 +6728,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6757,16 +6757,16 @@
         <v>110</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6794,10 +6794,10 @@
         <v>195</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6815,7 +6815,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6830,7 +6830,7 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>82</v>
@@ -6839,7 +6839,7 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6847,10 +6847,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6876,13 +6876,13 @@
         <v>110</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6911,10 +6911,10 @@
         <v>195</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -6932,7 +6932,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6947,7 +6947,7 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>82</v>
@@ -6956,7 +6956,7 @@
         <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6964,10 +6964,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6993,16 +6993,16 @@
         <v>180</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7051,7 +7051,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7066,7 +7066,7 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
@@ -7075,7 +7075,7 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7083,10 +7083,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7112,13 +7112,13 @@
         <v>180</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7168,7 +7168,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7183,7 +7183,7 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>82</v>
@@ -7192,7 +7192,7 @@
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7200,14 +7200,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7229,13 +7229,13 @@
         <v>180</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7285,7 +7285,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7300,7 +7300,7 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>82</v>
@@ -7309,7 +7309,7 @@
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7317,14 +7317,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7346,13 +7346,13 @@
         <v>180</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7402,7 +7402,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7417,7 +7417,7 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>82</v>
@@ -7426,7 +7426,7 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7434,14 +7434,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7463,13 +7463,13 @@
         <v>180</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7519,7 +7519,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7534,7 +7534,7 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>82</v>
@@ -7543,7 +7543,7 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7551,14 +7551,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7580,13 +7580,13 @@
         <v>180</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7636,7 +7636,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7651,7 +7651,7 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>82</v>
@@ -7660,7 +7660,7 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7668,10 +7668,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7697,13 +7697,13 @@
         <v>180</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7753,7 +7753,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7768,7 +7768,7 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>82</v>
@@ -7777,7 +7777,7 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7785,10 +7785,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7814,16 +7814,16 @@
         <v>227</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7872,7 +7872,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7887,7 +7887,7 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>82</v>
@@ -7896,7 +7896,7 @@
         <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7904,10 +7904,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7933,16 +7933,16 @@
         <v>201</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7970,10 +7970,10 @@
         <v>206</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -7991,7 +7991,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8006,16 +8006,16 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8023,10 +8023,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8049,19 +8049,19 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8110,7 +8110,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8125,7 +8125,7 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>184</v>
@@ -8134,7 +8134,7 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8142,10 +8142,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8168,19 +8168,19 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8229,7 +8229,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8244,7 +8244,7 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>184</v>
@@ -8253,7 +8253,7 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8261,10 +8261,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8287,19 +8287,19 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8348,7 +8348,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8360,10 +8360,10 @@
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>184</v>
@@ -8380,10 +8380,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8495,10 +8495,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8612,14 +8612,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8641,10 +8641,10 @@
         <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>166</v>
@@ -8699,7 +8699,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8731,10 +8731,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8760,16 +8760,16 @@
         <v>201</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8797,10 +8797,10 @@
         <v>206</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -8818,7 +8818,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8833,7 +8833,7 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>184</v>
@@ -8842,7 +8842,7 @@
         <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8850,10 +8850,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8876,17 +8876,17 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -8935,7 +8935,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8950,7 +8950,7 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>488</v>
+        <v>257</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>184</v>
@@ -8993,7 +8993,7 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L58" t="s" s="2">
         <v>491</v>
@@ -9069,7 +9069,7 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>184</v>
@@ -9112,7 +9112,7 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L59" t="s" s="2">
         <v>497</v>
@@ -9186,7 +9186,7 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>184</v>
@@ -9232,7 +9232,7 @@
         <v>110</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M60" t="s" s="2">
         <v>502</v>
@@ -9267,10 +9267,10 @@
         <v>195</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9303,7 +9303,7 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>184</v>
@@ -9580,7 +9580,7 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L63" t="s" s="2">
         <v>518</v>
@@ -9912,7 +9912,7 @@
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9934,10 +9934,10 @@
         <v>135</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>166</v>
@@ -9992,7 +9992,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10524,7 +10524,7 @@
         <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L71" t="s" s="2">
         <v>557</v>
@@ -10856,7 +10856,7 @@
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10878,10 +10878,10 @@
         <v>135</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>166</v>
@@ -10936,7 +10936,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>

--- a/jpcore-r4/main/StructureDefinition-jp-patient.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-patient.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-patient.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2879" uniqueCount="578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2879" uniqueCount="577">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -272,11 +272,11 @@
     <t>医療サービスを受けている個人または動物に関する情報</t>
   </si>
   <si>
-    <t>ケアまたはその他の健康関連サービスを受けている個人または動物に関する人口統計およびその他の管理情報。</t>
+    <t>ケアまたはその他の健康関連サービスを受けている個人または動物に関する基本情報およびその他の管理情報。</t>
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Patient[classCode=PAT]</t>
@@ -462,7 +462,7 @@
     <t>religion</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {patient-religion}
+    <t xml:space="preserve">Extension {patient-religion|4.0.1}
 </t>
   </si>
   <si>
@@ -479,8 +479,8 @@
 など</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t xml:space="preserve">ele-1
+</t>
   </si>
   <si>
     <t>Patient.extension:birthPlace</t>
@@ -489,7 +489,7 @@
     <t>birthPlace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {patient-birthPlace}
+    <t xml:space="preserve">Extension {patient-birthPlace|4.0.1}
 </t>
   </si>
   <si>
@@ -529,10 +529,6 @@
 など</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>Patient.modifierExtension</t>
   </si>
   <si>
@@ -902,7 +898,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Patient.telecom.system</t>
@@ -1385,13 +1381,13 @@
     <t>Patient.address.country</t>
   </si>
   <si>
-    <t>国名またはISO 3166コード　(ISO 3166 2 or 3文字こーど)</t>
+    <t>国名またはISO 3166コード　(ISO 3166 2 or 3文字コード)</t>
   </si>
   <si>
     <t>国-一般的に理解されている、または一般的に受け入れられている国の国名かコード。</t>
   </si>
   <si>
-    <t>ISO 3166 3文字コードは、人間が読める国名の代わりに使用する。  ISO 3166の2文字または3文字のコード.  日本であれば、jpまたはjpn</t>
+    <t>ISO 3166 3文字コードは、人間が読める国名の代わりに使用する。  ISO 3166の2文字または3文字のコード.  日本であれば、JPまたはJPN</t>
   </si>
   <si>
     <t>Address.country</t>
@@ -3401,10 +3397,10 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>82</v>
+        <v>148</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>82</v>
@@ -3520,10 +3516,10 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>82</v>
+        <v>148</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>82</v>
@@ -3639,7 +3635,7 @@
         <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>141</v>
@@ -3662,14 +3658,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3691,16 +3687,16 @@
         <v>135</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="N13" t="s" s="2">
+      <c r="O13" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>82</v>
@@ -3749,7 +3745,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3781,10 +3777,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3807,19 +3803,19 @@
         <v>91</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="N14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>82</v>
@@ -3868,7 +3864,7 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3883,16 +3879,16 @@
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AM14" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>82</v>
@@ -3900,10 +3896,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3926,13 +3922,13 @@
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3983,7 +3979,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3998,7 +3994,7 @@
         <v>82</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>82</v>
@@ -4015,14 +4011,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4044,13 +4040,13 @@
         <v>135</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="M16" t="s" s="2">
-        <v>187</v>
-      </c>
       <c r="N16" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4091,7 +4087,7 @@
         <v>138</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>82</v>
@@ -4100,7 +4096,7 @@
         <v>139</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4115,7 +4111,7 @@
         <v>141</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>82</v>
@@ -4132,10 +4128,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4161,16 +4157,16 @@
         <v>110</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
@@ -4195,31 +4191,31 @@
         <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="Y17" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Z17" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="Z17" t="s" s="2">
+      <c r="AA17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4234,7 +4230,7 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>82</v>
@@ -4251,10 +4247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4277,19 +4273,19 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>82</v>
@@ -4314,31 +4310,31 @@
         <v>82</v>
       </c>
       <c r="X18" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="Y18" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="Y18" t="s" s="2">
+      <c r="Z18" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="Z18" t="s" s="2">
+      <c r="AA18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF18" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4353,7 +4349,7 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>82</v>
@@ -4362,7 +4358,7 @@
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4370,10 +4366,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4399,16 +4395,16 @@
         <v>104</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4457,7 +4453,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4472,16 +4468,16 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4489,10 +4485,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4515,16 +4511,16 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4574,7 +4570,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4589,16 +4585,16 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4606,10 +4602,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4632,16 +4628,16 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4691,7 +4687,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4706,16 +4702,16 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>82</v>
@@ -4723,10 +4719,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4749,16 +4745,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4808,7 +4804,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4823,16 +4819,16 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -4840,10 +4836,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4866,26 +4862,26 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="N23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="O23" t="s" s="2">
+      <c r="P23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q23" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="P23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q23" t="s" s="2">
-        <v>248</v>
-      </c>
       <c r="R23" t="s" s="2">
         <v>82</v>
       </c>
@@ -4929,7 +4925,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4944,13 +4940,13 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>82</v>
@@ -4961,10 +4957,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4987,19 +4983,19 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -5048,7 +5044,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5063,16 +5059,16 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AM24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -5080,10 +5076,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5106,19 +5102,19 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5167,7 +5163,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5182,16 +5178,16 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AM25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
@@ -5199,10 +5195,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5225,13 +5221,13 @@
         <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5282,7 +5278,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5297,7 +5293,7 @@
         <v>82</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>82</v>
@@ -5314,14 +5310,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5343,13 +5339,13 @@
         <v>135</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5390,7 +5386,7 @@
         <v>138</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>82</v>
@@ -5399,7 +5395,7 @@
         <v>139</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5411,10 +5407,10 @@
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>82</v>
@@ -5431,10 +5427,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5460,13 +5456,13 @@
         <v>110</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5492,31 +5488,31 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="Z28" t="s" s="2">
+      <c r="AA28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5525,22 +5521,22 @@
         <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AJ28" t="s" s="2">
+      <c r="AK28" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AK28" t="s" s="2">
+      <c r="AL28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -5548,10 +5544,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5574,19 +5570,19 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5635,7 +5631,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5647,19 +5643,19 @@
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5667,10 +5663,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5696,16 +5692,16 @@
         <v>110</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5730,31 +5726,31 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Y30" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="Z30" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="Z30" t="s" s="2">
+      <c r="AA30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5766,19 +5762,19 @@
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -5786,10 +5782,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5812,16 +5808,16 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5871,7 +5867,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5883,10 +5879,10 @@
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>82</v>
@@ -5895,7 +5891,7 @@
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5903,10 +5899,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5929,16 +5925,16 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5988,7 +5984,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6000,10 +5996,10 @@
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>82</v>
@@ -6020,10 +6016,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6049,16 +6045,16 @@
         <v>110</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6083,14 +6079,14 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Y33" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="Z33" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="Z33" t="s" s="2">
-        <v>325</v>
-      </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
       </c>
@@ -6107,7 +6103,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6122,16 +6118,16 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6139,10 +6135,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6165,19 +6161,19 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="M34" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6226,7 +6222,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6241,27 +6237,27 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AM34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="AM34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>337</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6284,19 +6280,19 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6345,7 +6341,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6360,16 +6356,16 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6377,10 +6373,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6403,19 +6399,19 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6464,7 +6460,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6479,16 +6475,16 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AL36" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AL36" t="s" s="2">
+      <c r="AM36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6496,10 +6492,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6522,13 +6518,13 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6579,7 +6575,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6594,7 +6590,7 @@
         <v>82</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>82</v>
@@ -6611,14 +6607,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6640,13 +6636,13 @@
         <v>135</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="M38" t="s" s="2">
-        <v>187</v>
-      </c>
       <c r="N38" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6687,7 +6683,7 @@
         <v>138</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>82</v>
@@ -6696,7 +6692,7 @@
         <v>139</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6711,7 +6707,7 @@
         <v>141</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>82</v>
@@ -6728,10 +6724,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6757,16 +6753,16 @@
         <v>110</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6791,31 +6787,31 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="Z39" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="Z39" t="s" s="2">
+      <c r="AA39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF39" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6830,7 +6826,7 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>82</v>
@@ -6839,7 +6835,7 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6847,10 +6843,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6876,13 +6872,13 @@
         <v>110</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6908,31 +6904,31 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="Z40" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="Z40" t="s" s="2">
+      <c r="AA40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6947,7 +6943,7 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>82</v>
@@ -6956,7 +6952,7 @@
         <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6964,10 +6960,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6990,19 +6986,19 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7051,7 +7047,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7066,16 +7062,16 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7083,10 +7079,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7109,16 +7105,16 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7168,7 +7164,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7183,16 +7179,16 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7200,14 +7196,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7226,16 +7222,16 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7285,7 +7281,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7300,16 +7296,16 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7317,14 +7313,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7343,16 +7339,16 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7402,7 +7398,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7417,16 +7413,16 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7434,14 +7430,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7460,16 +7456,16 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7519,7 +7515,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7534,16 +7530,16 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7551,14 +7547,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7577,16 +7573,16 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7636,7 +7632,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7651,16 +7647,16 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7668,10 +7664,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7694,16 +7690,16 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7753,7 +7749,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7768,16 +7764,16 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7785,10 +7781,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7811,19 +7807,19 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="M48" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7872,7 +7868,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7887,7 +7883,7 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>82</v>
@@ -7896,7 +7892,7 @@
         <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7904,10 +7900,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7930,19 +7926,19 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7967,14 +7963,14 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="Z49" t="s" s="2">
-        <v>440</v>
-      </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
       </c>
@@ -7991,7 +7987,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8006,16 +8002,16 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AL49" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="AL49" t="s" s="2">
+      <c r="AM49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8023,10 +8019,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8049,19 +8045,19 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8110,7 +8106,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8125,16 +8121,16 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8142,10 +8138,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8168,19 +8164,19 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8229,7 +8225,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8244,16 +8240,16 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8261,10 +8257,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8287,19 +8283,19 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8348,7 +8344,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8360,13 +8356,13 @@
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AK52" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AK52" t="s" s="2">
-        <v>467</v>
-      </c>
       <c r="AL52" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>82</v>
@@ -8380,10 +8376,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8406,13 +8402,13 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8463,7 +8459,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8478,7 +8474,7 @@
         <v>82</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
@@ -8495,14 +8491,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8524,13 +8520,13 @@
         <v>135</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="M54" t="s" s="2">
-        <v>187</v>
-      </c>
       <c r="N54" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8580,7 +8576,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8595,7 +8591,7 @@
         <v>141</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>82</v>
@@ -8612,14 +8608,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8641,16 +8637,16 @@
         <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M55" t="s" s="2">
-        <v>473</v>
-      </c>
       <c r="N55" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="O55" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8699,7 +8695,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8731,10 +8727,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8757,19 +8753,19 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8794,14 +8790,14 @@
         <v>82</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Y56" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="Z56" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="Z56" t="s" s="2">
-        <v>481</v>
-      </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
       </c>
@@ -8818,7 +8814,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8833,16 +8829,16 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8850,10 +8846,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8876,17 +8872,17 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -8935,7 +8931,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8950,16 +8946,16 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -8967,10 +8963,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8993,19 +8989,19 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9054,7 +9050,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9069,16 +9065,16 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9086,10 +9082,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9112,17 +9108,17 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9171,7 +9167,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9186,16 +9182,16 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9203,10 +9199,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9232,14 +9228,14 @@
         <v>110</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9264,14 +9260,14 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="Z60" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="Z60" t="s" s="2">
-        <v>325</v>
-      </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9288,7 +9284,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9303,16 +9299,16 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9320,10 +9316,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9346,19 +9342,19 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9407,7 +9403,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9416,22 +9412,22 @@
         <v>90</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9439,10 +9435,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9465,13 +9461,13 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9522,7 +9518,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9537,10 +9533,10 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>82</v>
@@ -9554,10 +9550,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9580,19 +9576,19 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9641,7 +9637,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9656,10 +9652,10 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AL63" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>82</v>
@@ -9673,10 +9669,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9699,13 +9695,13 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9756,7 +9752,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9771,7 +9767,7 @@
         <v>82</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>82</v>
@@ -9788,14 +9784,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9817,13 +9813,13 @@
         <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="M65" t="s" s="2">
-        <v>187</v>
-      </c>
       <c r="N65" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9873,7 +9869,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9888,7 +9884,7 @@
         <v>141</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>82</v>
@@ -9905,14 +9901,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9934,16 +9930,16 @@
         <v>135</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M66" t="s" s="2">
-        <v>473</v>
-      </c>
       <c r="N66" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="O66" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -9992,7 +9988,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10024,10 +10020,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10050,19 +10046,19 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10111,7 +10107,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>90</v>
@@ -10126,16 +10122,16 @@
         <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AL67" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="AL67" t="s" s="2">
+      <c r="AM67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10143,10 +10139,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10169,19 +10165,19 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10230,7 +10226,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10245,16 +10241,16 @@
         <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AL68" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="AL68" t="s" s="2">
+      <c r="AM68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10262,14 +10258,14 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10288,16 +10284,16 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10347,7 +10343,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10362,16 +10358,16 @@
         <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10379,10 +10375,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10405,19 +10401,19 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10466,7 +10462,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10481,10 +10477,10 @@
         <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>82</v>
@@ -10498,10 +10494,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10524,19 +10520,19 @@
         <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -10585,7 +10581,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10600,10 +10596,10 @@
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>82</v>
@@ -10617,10 +10613,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10643,13 +10639,13 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10700,7 +10696,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10715,7 +10711,7 @@
         <v>82</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>82</v>
@@ -10732,14 +10728,14 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10761,13 +10757,13 @@
         <v>135</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="M73" t="s" s="2">
-        <v>187</v>
-      </c>
       <c r="N73" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10817,7 +10813,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10832,7 +10828,7 @@
         <v>141</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>82</v>
@@ -10849,14 +10845,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10878,16 +10874,16 @@
         <v>135</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M74" t="s" s="2">
-        <v>473</v>
-      </c>
       <c r="N74" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="O74" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -10936,7 +10932,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -10968,10 +10964,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10994,16 +10990,16 @@
         <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11053,7 +11049,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>90</v>
@@ -11068,16 +11064,16 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11085,10 +11081,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11114,13 +11110,13 @@
         <v>110</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11146,14 +11142,14 @@
         <v>82</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Y76" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="Z76" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="Z76" t="s" s="2">
-        <v>576</v>
-      </c>
       <c r="AA76" t="s" s="2">
         <v>82</v>
       </c>
@@ -11170,7 +11166,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>90</v>
@@ -11185,10 +11181,10 @@
         <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>82</v>

--- a/jpcore-r4/main/StructureDefinition-jp-patient.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-patient.xlsx
@@ -2204,17 +2204,17 @@
   <dimension ref="A1:AO76"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="39.47265625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="39.47265625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="33.83984375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="33.83984375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="176.609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="151.41015625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2223,27 +2223,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="155.12109375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="51.921875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="132.98828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="44.51171875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="156.828125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="40.8125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.3984375" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="40.0703125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="134.453125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="34.98828125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="92.07421875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="34.35546875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/main/StructureDefinition-jp-patient.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/main/StructureDefinition-jp-patient.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-patient.xlsx
@@ -371,7 +371,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -677,7 +677,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1446,7 +1446,7 @@
     <t>人の国内パートナーシップの状況。 / The domestic partnership status of a person.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/marital-status</t>
+    <t>http://hl7.org/fhir/ValueSet/marital-status|4.0.1</t>
   </si>
   <si>
     <t>player[classCode=PSN]/maritalStatusCode</t>
@@ -1590,7 +1590,7 @@
     <t>その患者の患者と接触者との関係の性質。 / The nature of the relationship between a patient and a contact person for that patient.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship</t>
+    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship|4.0.1</t>
   </si>
   <si>
     <t>code</t>
@@ -2229,7 +2229,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="132.98828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="44.51171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.33203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/main/StructureDefinition-jp-patient.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-patient.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
